--- a/seed/question-bank/source/TPL-002_Internal_Data_Handlers.xlsx
+++ b/seed/question-bank/source/TPL-002_Internal_Data_Handlers.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="15" customWidth="1" min="1" max="1"/>
@@ -614,7 +614,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>c0000004-b000-0000-0000-000000000001</t>
+          <t>d0000001-b000-0000-0000-000000000001</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -624,12 +624,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0.4</t>
+          <t>B0.3a</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>From whom is the data collected?</t>
+          <t>Is it in-house or third-party/vendor-hosted?</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Flags S.9 children data</t>
+          <t>Surfaces shadow IT / vendor risk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -657,7 +657,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>c0000005-b000-0000-0000-000000000001</t>
+          <t>d0000004-b000-0000-0000-000000000001</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -667,17 +667,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0.6</t>
+          <t>B0.3c</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Who inside the department has access, and is access on a least-privilege basis?</t>
+          <t>What security measures are implemented? (e.g., encryption at rest/in transit, access controls/MFA, audit logs, vulnerability assessments, data backup, breach detection)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MATURITY</t>
+          <t>FREE_TEXT</t>
         </is>
       </c>
       <c r="F6" s="1" t="inlineStr"/>
@@ -688,7 +688,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Access governance</t>
+          <t>Rule 6, A8 security safeguards</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -700,7 +700,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>c0000006-b000-0000-0000-000000000001</t>
+          <t>c0000004-b000-0000-0000-000000000001</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -710,17 +710,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0.7</t>
+          <t>B0.4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Do you export, download, or keep local copies (laptops, USB, email, personal drives)?</t>
+          <t>From whom is the data collected?</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BINARY_PLUS</t>
+          <t>SINGLE_SELECT</t>
         </is>
       </c>
       <c r="F7" s="1" t="inlineStr"/>
@@ -731,7 +731,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>High leakage risk</t>
+          <t>Flags S.9 children data</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -743,7 +743,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>c0000007-b000-0000-0000-000000000001</t>
+          <t>d0000002-b000-0000-0000-000000000001</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -753,12 +753,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0.8</t>
+          <t>B0.5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Do you share this data with other internal departments?</t>
+          <t>Does your department process personal data of vulnerable data principals (e.g., children, persons with disabilities) under DPDP?</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Internal data-flow map</t>
+          <t>S.9 vulnerable data principals</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -786,7 +786,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>c0000008-b000-0000-0000-000000000001</t>
+          <t>c0000005-b000-0000-0000-000000000001</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -796,17 +796,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0.9</t>
+          <t>B0.6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Do you share this data with external parties/vendors? Name them.</t>
+          <t>Who inside the department has access, and is access on a least-privilege basis?</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FREE_TEXT</t>
+          <t>MATURITY</t>
         </is>
       </c>
       <c r="F9" s="1" t="inlineStr"/>
@@ -817,7 +817,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Feeds Track C</t>
+          <t>Access governance</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -829,7 +829,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>c0000009-b000-0000-0000-000000000001</t>
+          <t>c0000006-b000-0000-0000-000000000001</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -839,17 +839,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0.10</t>
+          <t>B0.7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>How long does your department retain the data, and is there a deletion practice?</t>
+          <t>Do you export, download, or keep local copies (laptops, USB, email, personal drives)?</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MATURITY</t>
+          <t>BINARY_PLUS</t>
         </is>
       </c>
       <c r="F10" s="1" t="inlineStr"/>
@@ -860,7 +860,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Drives A7</t>
+          <t>High leakage risk</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -872,7 +872,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>c0000010-b000-0000-0000-000000000001</t>
+          <t>c0000007-b000-0000-0000-000000000001</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -882,12 +882,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0.12</t>
+          <t>B0.8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Have staff in your department completed DPDP/privacy training?</t>
+          <t>Do you share this data with other internal departments?</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Links A13</t>
+          <t>Internal data-flow map</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -915,7 +915,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>c0000011-b000-0000-0000-000000000001</t>
+          <t>c0000008-b000-0000-0000-000000000001</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -925,17 +925,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0.13</t>
+          <t>B0.9</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Are there documented procedures (SOPs) for handling PII in your function?</t>
+          <t>Do you share this data with external parties/vendors? Name them.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MATURITY</t>
+          <t>FREE_TEXT</t>
         </is>
       </c>
       <c r="F12" s="1" t="inlineStr"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Defined vs ad-hoc</t>
+          <t>Feeds Track C</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -958,7 +958,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>c0000012-b000-0000-0000-000000000001</t>
+          <t>c0000009-b000-0000-0000-000000000001</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -968,17 +968,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0.14</t>
+          <t>B0.10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Have you experienced any near-miss/incident involving personal data in the last 12 months?</t>
+          <t>How long does your department retain the data, and is there a deletion practice?</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BINARY_PLUS</t>
+          <t>MATURITY</t>
         </is>
       </c>
       <c r="F13" s="1" t="inlineStr"/>
@@ -989,7 +989,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Breach readiness signal</t>
+          <t>Drives A7</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1001,7 +1001,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>c0000013-b000-0000-0000-000000000001</t>
+          <t>d0000003-b000-0000-0000-000000000001</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0.15</t>
+          <t>B0.11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Do you use any AI / automated decisioning on personal data?</t>
+          <t>Does your department transfer personal data outside India?</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Flags SDF algo due-diligence</t>
+          <t>S.16, A10 cross-border</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1044,22 +1044,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>c0000002-b300-0000-0000-000000000001</t>
+          <t>c0000010-b000-0000-0000-000000000001</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Marketing / Digital / Growth</t>
+          <t>Common Module — All Departments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B3.2</t>
+          <t>B0.12</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Do you use cookies/trackers/pixels, and is consent obtained where required?</t>
+          <t>Have staff in your department completed DPDP/privacy training?</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1075,10 +1075,1945 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>Links A13</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>c0000011-b000-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Common Module — All Departments</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>B0.13</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Are there documented procedures (SOPs) for handling PII in your function?</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>MATURITY</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Defined vs ad-hoc</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>c0000012-b000-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Common Module — All Departments</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>B0.14</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Have you experienced any near-miss/incident involving personal data in the last 12 months?</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>BINARY_PLUS</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Breach readiness signal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>c0000013-b000-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Common Module — All Departments</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>B0.15</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Do you use any AI / automated decisioning on personal data?</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>BINARY_PLUS</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Flags SDF algo due-diligence</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>c0000001-b100-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Human Resources</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>B1.1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Do you collect candidate data and how long is unsuccessful-candidate data kept?</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>BINARY_PLUS</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>S.8(7), Rule 8</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>c0000002-b100-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Human Resources</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>B1.2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Do you conduct background verification / use third-party screening agencies?</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>BINARY_PLUS</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>S.8(2), Track C</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>c0000003-b100-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Human Resources</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>B1.3</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Do you process biometric data (attendance, access control)?</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>BINARY_PLUS</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>S.9, Rule 6</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>c0000004-b100-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Human Resources</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>B1.4</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Is employee health, payroll, bank, PF/ESI, and tax data access-restricted?</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>MATURITY</t>
+        </is>
+      </c>
+      <c r="F22" s="1" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Rule 6(b)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>c0000005-b100-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Human Resources</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>B1.5</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Are exit processes deactivating access and handling employee-record retention defined?</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>MATURITY</t>
+        </is>
+      </c>
+      <c r="F23" s="1" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>S.8(7), Rule 8</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>c0000006-b100-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Human Resources</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>B1.6</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Do you transfer employee data to a parent/group entity or overseas HR system?</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>BINARY_PLUS</t>
+        </is>
+      </c>
+      <c r="F24" s="1" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>S.16, A10</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>c0000001-b200-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>IT / Information Security</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>B2.1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Do you maintain the asset/system inventory holding PII and its data classification?</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>MATURITY</t>
+        </is>
+      </c>
+      <c r="F25" s="1" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Rule 6, A2.4</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>c0000002-b200-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>IT / Information Security</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>B2.2</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Are encryption, MFA, RBAC, and logging (1-yr retention) enforced across PII systems?</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>MATURITY</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Rule 6, A8</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>c0000003-b200-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>IT / Information Security</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>B2.3</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Is there centralised log monitoring/SIEM with alerting for unauthorised PII access?</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>MATURITY</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Rule 6(c), A8.3</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>c0000004-b200-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>IT / Information Security</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>B2.4</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Are backups encrypted and tested, and does deletion cascade to backups?</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>MATURITY</t>
+        </is>
+      </c>
+      <c r="F28" s="1" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Rule 6(d), A7.5</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>c0000005-b200-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>IT / Information Security</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>B2.5</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Is there a patch/vulnerability management and VAPT cadence for PII-bearing systems?</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>MATURITY</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Rule 6, A8.8</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>c0000006-b200-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>IT / Information Security</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>B2.6</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Do you provision/deprovision access on joiners-movers-leavers within SLA?</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>MATURITY</t>
+        </is>
+      </c>
+      <c r="F30" s="1" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Rule 6(b)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>c0000007-b200-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>IT / Information Security</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>B2.7</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Are admin/privileged accounts vaulted and monitored (PAM)?</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>MATURITY</t>
+        </is>
+      </c>
+      <c r="F31" s="1" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Rule 6(b)(c)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>c0000001-b300-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Marketing / Digital / Growth</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>B3.1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Do you collect leads/contacts and is consent captured with a compliant notice?</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>BINARY_PLUS</t>
+        </is>
+      </c>
+      <c r="F32" s="1" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>S.5, S.6, A3</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>c0000002-b300-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Marketing / Digital / Growth</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>B3.2</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Do you use cookies/trackers/pixels, and is consent obtained where required?</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>BINARY_PLUS</t>
+        </is>
+      </c>
+      <c r="F33" s="1" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
           <t>S.6, Rule 3</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>c0000003-b300-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Marketing / Digital / Growth</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>B3.3</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Do you run targeted advertising and ensure none targets children?</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>BINARY_PLUS</t>
+        </is>
+      </c>
+      <c r="F34" s="1" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>S.9(3), A4.2</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>c0000004-b300-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Marketing / Digital / Growth</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>B3.4</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Which third-party martech/CRM/email tools hold contact data?</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>FREE_TEXT</t>
+        </is>
+      </c>
+      <c r="F35" s="1" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>S.8(2), Track C</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>c0000005-b300-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Marketing / Digital / Growth</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>B3.5</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Can you honour opt-out/consent-withdrawal across all marketing channels?</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>BINARY_PLUS</t>
+        </is>
+      </c>
+      <c r="F36" s="1" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>S.6(4), A3.4</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>c0000006-b300-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Marketing / Digital / Growth</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>B3.6</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Do you buy/enrich contact lists from external data brokers?</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>BINARY_PLUS</t>
+        </is>
+      </c>
+      <c r="F37" s="1" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>S.4, S.5, A3</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>c0000001-b400-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Sales / Customer Success</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>B4.1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>What customer/prospect PII is held in CRM and who can export it?</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>SINGLE_SELECT</t>
+        </is>
+      </c>
+      <c r="F38" s="1" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Rule 6(b)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>c0000002-b400-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Sales / Customer Success</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>B4.2</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Are call recordings/chat transcripts captured, with notice and retention rules?</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>BINARY_PLUS</t>
+        </is>
+      </c>
+      <c r="F39" s="1" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>S.5, Rule 8</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>c0000003-b400-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Sales / Customer Success</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>B4.3</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Is customer data shared with channel partners/resellers under contract?</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>BINARY_PLUS</t>
+        </is>
+      </c>
+      <c r="F40" s="1" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>S.8(2), Track C</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>c0000001-b500-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Finance / Accounts</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>B5.1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Do you process payment, bank, KYC, PAN/Aadhaar, or tax data?</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>SINGLE_SELECT</t>
+        </is>
+      </c>
+      <c r="F41" s="1" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>S.8 risk basis</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>c0000002-b500-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Finance / Accounts</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>B5.2</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Are statutory retention obligations reconciled with DPDP minimisation/erasure?</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>MATURITY</t>
+        </is>
+      </c>
+      <c r="F42" s="1" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>S.8(7), Rule 8</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>c0000003-b500-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Finance / Accounts</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>B5.3</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Which payment processors / banking integrations receive PII?</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>FREE_TEXT</t>
+        </is>
+      </c>
+      <c r="F43" s="1" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>S.8(2), Track C</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>c0000004-b500-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Finance / Accounts</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>B5.4</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Is sensitive financial data masked/tokenised in reports and screens?</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>MATURITY</t>
+        </is>
+      </c>
+      <c r="F44" s="1" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Rule 6(a), A8.1</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>c0000001-b600-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Customer Support / Operations</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>B6.1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>How are data-principal rights requests received and routed within SLA?</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>MATURITY</t>
+        </is>
+      </c>
+      <c r="F45" s="1" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Rule 14, A5.2</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>c0000002-b600-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Customer Support / Operations</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>B6.2</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Is the ticketing/helpdesk system access-controlled and is PII redacted where possible?</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>MATURITY</t>
+        </is>
+      </c>
+      <c r="F46" s="1" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Rule 6(b)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>c0000003-b600-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Customer Support / Operations</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>B6.3</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Are support transcripts/recordings retained per schedule and purged?</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>BINARY_PLUS</t>
+        </is>
+      </c>
+      <c r="F47" s="1" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Rule 8, A7</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>c0000001-b700-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Procurement / Vendor Management</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>B7.1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Is a DPDP/security due-diligence step mandatory before onboarding any vendor that touches PII?</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>BINARY_PLUS</t>
+        </is>
+      </c>
+      <c r="F48" s="1" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>S.8, Track C gate</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>c0000002-b700-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Procurement / Vendor Management</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>B7.2</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Do all such contracts include processor clauses (security, sub-processing, deletion, audit, breach SLA)?</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>BINARY_PLUS</t>
+        </is>
+      </c>
+      <c r="F49" s="1" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>S.8(2), Rule 6(f), A11.2</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>c0000003-b700-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Procurement / Vendor Management</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>B7.3</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Is there a maintained vendor register with risk tiers and review dates?</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>MATURITY</t>
+        </is>
+      </c>
+      <c r="F50" s="1" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>S.8(2), A11.1</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>c0000001-b800-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Product / Engineering</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>B8.1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Is privacy-by-design / data-minimisation enforced in design and code review?</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>MATURITY</t>
+        </is>
+      </c>
+      <c r="F51" s="1" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>S.8, A13.2</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>c0000002-b800-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Product / Engineering</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>B8.2</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Is PII excluded from logs, test/staging environments, and analytics where not needed?</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>MATURITY</t>
+        </is>
+      </c>
+      <c r="F52" s="1" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Rule 6</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>c0000003-b800-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Product / Engineering</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>B8.3</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Are consent, retention, and erasure enforceable at the data-model level?</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>MATURITY</t>
+        </is>
+      </c>
+      <c r="F53" s="1" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>S.8(7), A7</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>c0000004-b800-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Product / Engineering</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>B8.4</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Do features using AI/automated decisions on PII undergo a risk review?</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>BINARY_PLUS</t>
+        </is>
+      </c>
+      <c r="F54" s="1" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Rule 13, A12.4</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>c0000001-b900-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Legal / Compliance</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>B9.1</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Are notices, consent text, and contracts reviewed against current DPDP Rules?</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>MATURITY</t>
+        </is>
+      </c>
+      <c r="F55" s="1" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>S.5, S.6, Rule 3</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>c0000002-b900-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Legal / Compliance</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>B9.2</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Is regulatory change (Board directions, schedule updates) monitored and actioned?</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>MATURITY</t>
+        </is>
+      </c>
+      <c r="F56" s="1" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Ongoing compliance</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>c0000003-b900-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Legal / Compliance</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>B9.3</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Is the breach-notification legal workflow (Board + principals) defined?</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>MATURITY</t>
+        </is>
+      </c>
+      <c r="F57" s="1" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Rule 7, A9</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>c0000001-ba00-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Facilities / Physical Security</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>B10.1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Is physical access to areas/servers holding PII controlled and logged?</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>MATURITY</t>
+        </is>
+      </c>
+      <c r="F58" s="1" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Rule 6</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>c0000002-ba00-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Facilities / Physical Security</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>B10.2</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Are paper records with PII secured and disposed of securely?</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>MATURITY</t>
+        </is>
+      </c>
+      <c r="F59" s="1" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Rule 6</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>c0000003-ba00-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Facilities / Physical Security</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>B10.3</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Is CCTV/visitor data treated as PII with notice and retention rules?</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>BINARY_PLUS</t>
+        </is>
+      </c>
+      <c r="F60" s="1" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>S.5, Rule 8</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1086,39 +3021,165 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
-  <dataValidations count="11">
+  <dataValidations count="53">
     <dataValidation sqref="F3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
       <formula1>_options!$A$3:$D$3</formula1>
     </dataValidation>
     <dataValidation sqref="F5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
-      <formula1>_options!$A$5:$F$5</formula1>
-    </dataValidation>
-    <dataValidation sqref="F6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
-      <formula1>_options!$A$6:$E$6</formula1>
+      <formula1>_options!$A$5:$C$5</formula1>
     </dataValidation>
     <dataValidation sqref="F7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
-      <formula1>_options!$A$7:$D$7</formula1>
+      <formula1>_options!$A$7:$F$7</formula1>
     </dataValidation>
     <dataValidation sqref="F8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
       <formula1>_options!$A$8:$D$8</formula1>
     </dataValidation>
+    <dataValidation sqref="F9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$9:$E$9</formula1>
+    </dataValidation>
     <dataValidation sqref="F10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
-      <formula1>_options!$A$10:$E$10</formula1>
+      <formula1>_options!$A$10:$D$10</formula1>
     </dataValidation>
     <dataValidation sqref="F11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
       <formula1>_options!$A$11:$D$11</formula1>
     </dataValidation>
-    <dataValidation sqref="F12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
-      <formula1>_options!$A$12:$E$12</formula1>
-    </dataValidation>
     <dataValidation sqref="F13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
-      <formula1>_options!$A$13:$D$13</formula1>
+      <formula1>_options!$A$13:$E$13</formula1>
     </dataValidation>
     <dataValidation sqref="F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
       <formula1>_options!$A$14:$D$14</formula1>
     </dataValidation>
     <dataValidation sqref="F15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
       <formula1>_options!$A$15:$D$15</formula1>
+    </dataValidation>
+    <dataValidation sqref="F16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$16:$E$16</formula1>
+    </dataValidation>
+    <dataValidation sqref="F17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$17:$D$17</formula1>
+    </dataValidation>
+    <dataValidation sqref="F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$18:$D$18</formula1>
+    </dataValidation>
+    <dataValidation sqref="F19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$19:$D$19</formula1>
+    </dataValidation>
+    <dataValidation sqref="F20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$20:$D$20</formula1>
+    </dataValidation>
+    <dataValidation sqref="F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$21:$D$21</formula1>
+    </dataValidation>
+    <dataValidation sqref="F22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$22:$E$22</formula1>
+    </dataValidation>
+    <dataValidation sqref="F23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$23:$E$23</formula1>
+    </dataValidation>
+    <dataValidation sqref="F24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$24:$D$24</formula1>
+    </dataValidation>
+    <dataValidation sqref="F25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$25:$E$25</formula1>
+    </dataValidation>
+    <dataValidation sqref="F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$26:$E$26</formula1>
+    </dataValidation>
+    <dataValidation sqref="F27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$27:$E$27</formula1>
+    </dataValidation>
+    <dataValidation sqref="F28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$28:$E$28</formula1>
+    </dataValidation>
+    <dataValidation sqref="F29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$29:$E$29</formula1>
+    </dataValidation>
+    <dataValidation sqref="F30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$30:$E$30</formula1>
+    </dataValidation>
+    <dataValidation sqref="F31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$31:$E$31</formula1>
+    </dataValidation>
+    <dataValidation sqref="F32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$32:$D$32</formula1>
+    </dataValidation>
+    <dataValidation sqref="F33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$33:$D$33</formula1>
+    </dataValidation>
+    <dataValidation sqref="F34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$34:$D$34</formula1>
+    </dataValidation>
+    <dataValidation sqref="F36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$36:$D$36</formula1>
+    </dataValidation>
+    <dataValidation sqref="F37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$37:$D$37</formula1>
+    </dataValidation>
+    <dataValidation sqref="F38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$38:$C$38</formula1>
+    </dataValidation>
+    <dataValidation sqref="F39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$39:$D$39</formula1>
+    </dataValidation>
+    <dataValidation sqref="F40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$40:$D$40</formula1>
+    </dataValidation>
+    <dataValidation sqref="F41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$41:$C$41</formula1>
+    </dataValidation>
+    <dataValidation sqref="F42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$42:$E$42</formula1>
+    </dataValidation>
+    <dataValidation sqref="F44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$44:$E$44</formula1>
+    </dataValidation>
+    <dataValidation sqref="F45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$45:$E$45</formula1>
+    </dataValidation>
+    <dataValidation sqref="F46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$46:$E$46</formula1>
+    </dataValidation>
+    <dataValidation sqref="F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$47:$D$47</formula1>
+    </dataValidation>
+    <dataValidation sqref="F48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$48:$D$48</formula1>
+    </dataValidation>
+    <dataValidation sqref="F49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$49:$D$49</formula1>
+    </dataValidation>
+    <dataValidation sqref="F50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$50:$E$50</formula1>
+    </dataValidation>
+    <dataValidation sqref="F51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$51:$E$51</formula1>
+    </dataValidation>
+    <dataValidation sqref="F52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$52:$E$52</formula1>
+    </dataValidation>
+    <dataValidation sqref="F53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$53:$E$53</formula1>
+    </dataValidation>
+    <dataValidation sqref="F54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$54:$D$54</formula1>
+    </dataValidation>
+    <dataValidation sqref="F55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$55:$E$55</formula1>
+    </dataValidation>
+    <dataValidation sqref="F56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$56:$E$56</formula1>
+    </dataValidation>
+    <dataValidation sqref="F57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$57:$E$57</formula1>
+    </dataValidation>
+    <dataValidation sqref="F58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$58:$E$58</formula1>
+    </dataValidation>
+    <dataValidation sqref="F59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$59:$E$59</formula1>
+    </dataValidation>
+    <dataValidation sqref="F60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list" type="list">
+      <formula1>_options!$A$60:$D$60</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1131,7 +3192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:F15"/>
+  <dimension ref="A3:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="3">
@@ -1159,81 +3220,49 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>In-house</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>Third-party / Vendor-hosted</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Candidates</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Vendors</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Children</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>Mixed (both)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Customers</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Candidates</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>N-A</t>
+          <t>Vendors</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Children</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mixed</t>
         </is>
       </c>
     </row>
@@ -1259,30 +3288,52 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>N-A</t>
         </is>
       </c>
     </row>
@@ -1308,52 +3359,30 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>N-A</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1396,6 +3425,1057 @@
         </is>
       </c>
       <c r="D15" t="inlineStr">
+        <is>
+          <t>N-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>N-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>N-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>N-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>N-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>N-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>N-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>N-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>N-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>N-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>N-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>N-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Broad export</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Restricted export</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>No export controls</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>N-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>N-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Yes — one type</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Yes — multiple types</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>N-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>N-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>N-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>N-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
         <is>
           <t>N-A</t>
         </is>

--- a/seed/question-bank/source/TPL-002_Internal_Data_Handlers.xlsx
+++ b/seed/question-bank/source/TPL-002_Internal_Data_Handlers.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1043" uniqueCount="403">
   <si>
     <t>Question ID</t>
   </si>
@@ -1026,6 +1026,229 @@
 Backup and data retention handling procedure
 Final access review
 Sample completed vendor offboarding record</t>
+  </si>
+  <si>
+    <t>c0000001-bc00-0000-0000-000000000001</t>
+  </si>
+  <si>
+    <t>School Operations</t>
+  </si>
+  <si>
+    <t>B12.1</t>
+  </si>
+  <si>
+    <t>Is a parent's or lawful guardian's verifiable consent obtained before a student's personal data is processed on the basis of consent?</t>
+  </si>
+  <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>S.9(1), Rule 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admission form with the parental consent section
+Consent records for each student
+How the school checks that the person consenting is the parent or guardian and an adult</t>
+  </si>
+  <si>
+    <t>c0000002-bc00-0000-0000-000000000001</t>
+  </si>
+  <si>
+    <t>B12.2</t>
+  </si>
+  <si>
+    <t>Does the admission process collect only the student and parent data the school needs, with a notice that lists that data and its purposes?</t>
+  </si>
+  <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admission form
+Privacy notice for parents
+List of admission data fields with the purpose of each</t>
+  </si>
+  <si>
+    <t>c0000003-bc00-0000-0000-000000000001</t>
+  </si>
+  <si>
+    <t>B12.3</t>
+  </si>
+  <si>
+    <t>Is tracking or behavioural monitoring of students (classroom CCTV, bus GPS, attendance or learning apps) limited to educational activities and student safety?</t>
+  </si>
+  <si>
+    <t>S.9(3), S.9(4), Rule 12, Fourth Schedule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">List of monitoring and tracking in use, with the purpose of each
+CCTV and GPS policy
+Exemption register entry for each Fourth Schedule purpose relied on</t>
+  </si>
+  <si>
+    <t>c0000004-bc00-0000-0000-000000000001</t>
+  </si>
+  <si>
+    <t>B12.4</t>
+  </si>
+  <si>
+    <t>Are students' data kept from advertising, marketing and any use detrimental to their well-being, including promotions by ed-tech, uniform or book vendors?</t>
+  </si>
+  <si>
+    <t>S.9(2), S.9(3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policy on use of student data
+Vendor contracts with no-marketing clauses
+Declaration of no targeted advertising to students</t>
+  </si>
+  <si>
+    <t>c0000005-bc00-0000-0000-000000000001</t>
+  </si>
+  <si>
+    <t>B12.5</t>
+  </si>
+  <si>
+    <t>Is school transport data (routes, stops, pick-up times, GPS tracking, driver and attendant details) access-controlled and shared only with parents and authorised staff?</t>
+  </si>
+  <si>
+    <t>S.8(5), Rule 6, Fourth Schedule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transport app access list
+Transport vendor contract
+Driver and attendant verification records</t>
+  </si>
+  <si>
+    <t>c0000006-bc00-0000-0000-000000000001</t>
+  </si>
+  <si>
+    <t>B12.6</t>
+  </si>
+  <si>
+    <t>Are students' health records (medical room visits, allergies, vaccinations, special needs) kept confidential and open only to the staff who need them?</t>
+  </si>
+  <si>
+    <t>S.8(5), Rule 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medical room register and where it is kept
+Access list for health records
+Procedure for sharing health information with teachers</t>
+  </si>
+  <si>
+    <t>c0000007-bc00-0000-0000-000000000001</t>
+  </si>
+  <si>
+    <t>B12.7</t>
+  </si>
+  <si>
+    <t>Are counselling, disciplinary and child-protection (POCSO) records kept separately, with access restricted to the designated staff?</t>
+  </si>
+  <si>
+    <t>S.8(5), S.9(2), Rule 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Child protection policy
+Access list for counselling and incident records
+Storage arrangement for these records</t>
+  </si>
+  <si>
+    <t>c0000008-bc00-0000-0000-000000000001</t>
+  </si>
+  <si>
+    <t>B12.8</t>
+  </si>
+  <si>
+    <t>Are photos and videos of students published (website, social media, newsletters) only with parental consent, and taken down when consent is withdrawn?</t>
+  </si>
+  <si>
+    <t>S.6(4), S.9(1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Photo and video consent form
+Register of consents and withdrawals
+Take-down procedure</t>
+  </si>
+  <si>
+    <t>c0000009-bc00-0000-0000-000000000001</t>
+  </si>
+  <si>
+    <t>B12.9</t>
+  </si>
+  <si>
+    <t>Are student and parent records shared with boards, government portals and ed-tech or transport vendors only where a law requires it or under a contract?</t>
+  </si>
+  <si>
+    <t>S.7, S.8(2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">List of portals and vendors that receive student data, with the legal basis or contract for each
+Data processing agreements with vendors</t>
+  </si>
+  <si>
+    <t>c0000010-bc00-0000-0000-000000000001</t>
+  </si>
+  <si>
+    <t>B12.10</t>
+  </si>
+  <si>
+    <t>Is there a retention schedule for admission, academic, fee and transfer records, including applicants not admitted and students who have left?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retention schedule for student records
+Deletion or archival log
+Board or regulatory retention requirements relied on</t>
+  </si>
+  <si>
+    <t>c0000011-bc00-0000-0000-000000000001</t>
+  </si>
+  <si>
+    <t>B12.11</t>
+  </si>
+  <si>
+    <t>Can parents ask to see, correct or erase their child's data and raise grievances, and does the school verify that the request comes from the parent or guardian?</t>
+  </si>
+  <si>
+    <t>S.11-S.13, Rule 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rights request form or channel for parents
+Requester verification procedure
+Rights and grievance request log</t>
+  </si>
+  <si>
+    <t>c0000012-bc00-0000-0000-000000000001</t>
+  </si>
+  <si>
+    <t>B12.12</t>
+  </si>
+  <si>
+    <t>Are visitor, gate-pass and authorised pick-up records controlled and kept only as long as they are needed?</t>
+  </si>
+  <si>
+    <t>S.8(5), S.8(7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visitor and gate-pass register
+Authorised pick-up list procedure
+Retention period for these records</t>
+  </si>
+  <si>
+    <t>c0000013-bc00-0000-0000-000000000001</t>
+  </si>
+  <si>
+    <t>B12.13</t>
+  </si>
+  <si>
+    <t>Are student accounts on learning platforms and school apps set up without behavioural profiling or targeted advertising, and are the vendor terms checked for this?</t>
+  </si>
+  <si>
+    <t>S.9(3), S.8(2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">List of learning platforms and apps with student accounts
+Vendor terms or data processing agreements
+Platform privacy settings for students</t>
   </si>
   <si>
     <t>Consent</t>
@@ -1474,7 +1697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -3441,8 +3664,424 @@
         <v>313</v>
       </c>
     </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>314</v>
+      </c>
+      <c r="B62" t="s">
+        <v>315</v>
+      </c>
+      <c r="C62" t="s">
+        <v>316</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="E62" t="s">
+        <v>46</v>
+      </c>
+      <c r="F62" t="s">
+        <v>24</v>
+      </c>
+      <c r="G62" t="s">
+        <v>318</v>
+      </c>
+      <c r="H62" t="s">
+        <v>319</v>
+      </c>
+      <c r="I62" t="s">
+        <v>18</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>321</v>
+      </c>
+      <c r="B63" t="s">
+        <v>315</v>
+      </c>
+      <c r="C63" t="s">
+        <v>322</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="E63" t="s">
+        <v>40</v>
+      </c>
+      <c r="F63" t="s">
+        <v>24</v>
+      </c>
+      <c r="G63" t="s">
+        <v>324</v>
+      </c>
+      <c r="H63" t="s">
+        <v>268</v>
+      </c>
+      <c r="I63" t="s">
+        <v>18</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>326</v>
+      </c>
+      <c r="B64" t="s">
+        <v>315</v>
+      </c>
+      <c r="C64" t="s">
+        <v>327</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E64" t="s">
+        <v>40</v>
+      </c>
+      <c r="F64" t="s">
+        <v>24</v>
+      </c>
+      <c r="G64" t="s">
+        <v>318</v>
+      </c>
+      <c r="H64" t="s">
+        <v>329</v>
+      </c>
+      <c r="I64" t="s">
+        <v>18</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>331</v>
+      </c>
+      <c r="B65" t="s">
+        <v>315</v>
+      </c>
+      <c r="C65" t="s">
+        <v>332</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="E65" t="s">
+        <v>46</v>
+      </c>
+      <c r="F65" t="s">
+        <v>24</v>
+      </c>
+      <c r="G65" t="s">
+        <v>318</v>
+      </c>
+      <c r="H65" t="s">
+        <v>334</v>
+      </c>
+      <c r="I65" t="s">
+        <v>18</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>336</v>
+      </c>
+      <c r="B66" t="s">
+        <v>315</v>
+      </c>
+      <c r="C66" t="s">
+        <v>337</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="E66" t="s">
+        <v>40</v>
+      </c>
+      <c r="F66" t="s">
+        <v>24</v>
+      </c>
+      <c r="G66" t="s">
+        <v>324</v>
+      </c>
+      <c r="H66" t="s">
+        <v>339</v>
+      </c>
+      <c r="I66" t="s">
+        <v>18</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>341</v>
+      </c>
+      <c r="B67" t="s">
+        <v>315</v>
+      </c>
+      <c r="C67" t="s">
+        <v>342</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="E67" t="s">
+        <v>40</v>
+      </c>
+      <c r="F67" t="s">
+        <v>24</v>
+      </c>
+      <c r="G67" t="s">
+        <v>324</v>
+      </c>
+      <c r="H67" t="s">
+        <v>344</v>
+      </c>
+      <c r="I67" t="s">
+        <v>18</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>346</v>
+      </c>
+      <c r="B68" t="s">
+        <v>315</v>
+      </c>
+      <c r="C68" t="s">
+        <v>347</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E68" t="s">
+        <v>40</v>
+      </c>
+      <c r="F68" t="s">
+        <v>24</v>
+      </c>
+      <c r="G68" t="s">
+        <v>318</v>
+      </c>
+      <c r="H68" t="s">
+        <v>349</v>
+      </c>
+      <c r="I68" t="s">
+        <v>18</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>351</v>
+      </c>
+      <c r="B69" t="s">
+        <v>315</v>
+      </c>
+      <c r="C69" t="s">
+        <v>352</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E69" t="s">
+        <v>46</v>
+      </c>
+      <c r="F69" t="s">
+        <v>24</v>
+      </c>
+      <c r="G69" t="s">
+        <v>324</v>
+      </c>
+      <c r="H69" t="s">
+        <v>354</v>
+      </c>
+      <c r="I69" t="s">
+        <v>18</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>356</v>
+      </c>
+      <c r="B70" t="s">
+        <v>315</v>
+      </c>
+      <c r="C70" t="s">
+        <v>357</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="E70" t="s">
+        <v>46</v>
+      </c>
+      <c r="F70" t="s">
+        <v>24</v>
+      </c>
+      <c r="G70" t="s">
+        <v>324</v>
+      </c>
+      <c r="H70" t="s">
+        <v>359</v>
+      </c>
+      <c r="I70" t="s">
+        <v>18</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>361</v>
+      </c>
+      <c r="B71" t="s">
+        <v>315</v>
+      </c>
+      <c r="C71" t="s">
+        <v>362</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E71" t="s">
+        <v>40</v>
+      </c>
+      <c r="F71" t="s">
+        <v>24</v>
+      </c>
+      <c r="G71" t="s">
+        <v>324</v>
+      </c>
+      <c r="H71" t="s">
+        <v>88</v>
+      </c>
+      <c r="I71" t="s">
+        <v>18</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>365</v>
+      </c>
+      <c r="B72" t="s">
+        <v>315</v>
+      </c>
+      <c r="C72" t="s">
+        <v>366</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="E72" t="s">
+        <v>40</v>
+      </c>
+      <c r="F72" t="s">
+        <v>24</v>
+      </c>
+      <c r="G72" t="s">
+        <v>324</v>
+      </c>
+      <c r="H72" t="s">
+        <v>368</v>
+      </c>
+      <c r="I72" t="s">
+        <v>18</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>370</v>
+      </c>
+      <c r="B73" t="s">
+        <v>315</v>
+      </c>
+      <c r="C73" t="s">
+        <v>371</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="E73" t="s">
+        <v>40</v>
+      </c>
+      <c r="F73" t="s">
+        <v>24</v>
+      </c>
+      <c r="G73" t="s">
+        <v>16</v>
+      </c>
+      <c r="H73" t="s">
+        <v>373</v>
+      </c>
+      <c r="I73" t="s">
+        <v>18</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>375</v>
+      </c>
+      <c r="B74" t="s">
+        <v>315</v>
+      </c>
+      <c r="C74" t="s">
+        <v>376</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="E74" t="s">
+        <v>46</v>
+      </c>
+      <c r="F74" t="s">
+        <v>24</v>
+      </c>
+      <c r="G74" t="s">
+        <v>318</v>
+      </c>
+      <c r="H74" t="s">
+        <v>378</v>
+      </c>
+      <c r="I74" t="s">
+        <v>18</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>379</v>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations count="54">
+  <dataValidations count="67">
     <dataValidation type="list" allowBlank="1" sqref="F10">
       <formula1>_options!$A$10:$E$10</formula1>
     </dataValidation>
@@ -3599,8 +4238,47 @@
     <dataValidation type="list" allowBlank="1" sqref="F61">
       <formula1>_options!$A$61:$E$61</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F62">
+      <formula1>_options!$A$62:$D$62</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F63">
+      <formula1>_options!$A$63:$E$63</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F64">
+      <formula1>_options!$A$64:$E$64</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F65">
+      <formula1>_options!$A$65:$D$65</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F66">
+      <formula1>_options!$A$66:$E$66</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F67">
+      <formula1>_options!$A$67:$E$67</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F68">
+      <formula1>_options!$A$68:$E$68</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F69">
+      <formula1>_options!$A$69:$D$69</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="F7">
       <formula1>_options!$A$7:$D$7</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F70">
+      <formula1>_options!$A$70:$D$70</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F71">
+      <formula1>_options!$A$71:$E$71</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F72">
+      <formula1>_options!$A$72:$E$72</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F73">
+      <formula1>_options!$A$73:$E$73</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F74">
+      <formula1>_options!$A$74:$D$74</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="F8">
       <formula1>_options!$A$8:$D$8</formula1>
@@ -3613,480 +4291,480 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:F61"/>
+  <dimension ref="A3:F74"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>314</v>
+        <v>380</v>
       </c>
       <c r="B3" t="s">
-        <v>315</v>
+        <v>381</v>
       </c>
       <c r="C3" t="s">
-        <v>316</v>
+        <v>382</v>
       </c>
       <c r="D3" t="s">
-        <v>317</v>
+        <v>383</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>318</v>
+        <v>384</v>
       </c>
       <c r="B5" t="s">
-        <v>319</v>
+        <v>385</v>
       </c>
       <c r="C5" t="s">
-        <v>320</v>
+        <v>386</v>
       </c>
       <c r="D5" t="s">
-        <v>321</v>
+        <v>387</v>
       </c>
       <c r="E5" t="s">
-        <v>322</v>
+        <v>388</v>
       </c>
       <c r="F5" t="s">
-        <v>323</v>
+        <v>389</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="B6" t="s">
-        <v>325</v>
+        <v>391</v>
       </c>
       <c r="C6" t="s">
-        <v>326</v>
+        <v>392</v>
       </c>
       <c r="D6" t="s">
-        <v>327</v>
+        <v>393</v>
       </c>
       <c r="E6" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>329</v>
+        <v>395</v>
       </c>
       <c r="B7" t="s">
-        <v>330</v>
+        <v>396</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>331</v>
+        <v>397</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>329</v>
+        <v>395</v>
       </c>
       <c r="B8" t="s">
-        <v>330</v>
+        <v>396</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>331</v>
+        <v>397</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="B10" t="s">
-        <v>325</v>
+        <v>391</v>
       </c>
       <c r="C10" t="s">
-        <v>326</v>
+        <v>392</v>
       </c>
       <c r="D10" t="s">
-        <v>327</v>
+        <v>393</v>
       </c>
       <c r="E10" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>329</v>
+        <v>395</v>
       </c>
       <c r="B11" t="s">
-        <v>330</v>
+        <v>396</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>331</v>
+        <v>397</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="B12" t="s">
-        <v>325</v>
+        <v>391</v>
       </c>
       <c r="C12" t="s">
-        <v>326</v>
+        <v>392</v>
       </c>
       <c r="D12" t="s">
-        <v>327</v>
+        <v>393</v>
       </c>
       <c r="E12" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>329</v>
+        <v>395</v>
       </c>
       <c r="B13" t="s">
-        <v>330</v>
+        <v>396</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>331</v>
+        <v>397</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>329</v>
+        <v>395</v>
       </c>
       <c r="B14" t="s">
-        <v>330</v>
+        <v>396</v>
       </c>
       <c r="C14" t="s">
         <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>331</v>
+        <v>397</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>329</v>
+        <v>395</v>
       </c>
       <c r="B15" t="s">
-        <v>330</v>
+        <v>396</v>
       </c>
       <c r="C15" t="s">
         <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>331</v>
+        <v>397</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>329</v>
+        <v>395</v>
       </c>
       <c r="B16" t="s">
-        <v>330</v>
+        <v>396</v>
       </c>
       <c r="C16" t="s">
         <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>331</v>
+        <v>397</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>329</v>
+        <v>395</v>
       </c>
       <c r="B17" t="s">
-        <v>330</v>
+        <v>396</v>
       </c>
       <c r="C17" t="s">
         <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>331</v>
+        <v>397</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="B18" t="s">
-        <v>325</v>
+        <v>391</v>
       </c>
       <c r="C18" t="s">
-        <v>326</v>
+        <v>392</v>
       </c>
       <c r="D18" t="s">
-        <v>327</v>
+        <v>393</v>
       </c>
       <c r="E18" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="B19" t="s">
-        <v>325</v>
+        <v>391</v>
       </c>
       <c r="C19" t="s">
-        <v>326</v>
+        <v>392</v>
       </c>
       <c r="D19" t="s">
-        <v>327</v>
+        <v>393</v>
       </c>
       <c r="E19" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>329</v>
+        <v>395</v>
       </c>
       <c r="B20" t="s">
-        <v>330</v>
+        <v>396</v>
       </c>
       <c r="C20" t="s">
         <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>331</v>
+        <v>397</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="B21" t="s">
-        <v>325</v>
+        <v>391</v>
       </c>
       <c r="C21" t="s">
-        <v>326</v>
+        <v>392</v>
       </c>
       <c r="D21" t="s">
-        <v>327</v>
+        <v>393</v>
       </c>
       <c r="E21" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="B22" t="s">
-        <v>325</v>
+        <v>391</v>
       </c>
       <c r="C22" t="s">
-        <v>326</v>
+        <v>392</v>
       </c>
       <c r="D22" t="s">
-        <v>327</v>
+        <v>393</v>
       </c>
       <c r="E22" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="B23" t="s">
-        <v>325</v>
+        <v>391</v>
       </c>
       <c r="C23" t="s">
-        <v>326</v>
+        <v>392</v>
       </c>
       <c r="D23" t="s">
-        <v>327</v>
+        <v>393</v>
       </c>
       <c r="E23" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="B24" t="s">
-        <v>325</v>
+        <v>391</v>
       </c>
       <c r="C24" t="s">
-        <v>326</v>
+        <v>392</v>
       </c>
       <c r="D24" t="s">
-        <v>327</v>
+        <v>393</v>
       </c>
       <c r="E24" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="B25" t="s">
-        <v>325</v>
+        <v>391</v>
       </c>
       <c r="C25" t="s">
-        <v>326</v>
+        <v>392</v>
       </c>
       <c r="D25" t="s">
-        <v>327</v>
+        <v>393</v>
       </c>
       <c r="E25" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="B26" t="s">
-        <v>325</v>
+        <v>391</v>
       </c>
       <c r="C26" t="s">
-        <v>326</v>
+        <v>392</v>
       </c>
       <c r="D26" t="s">
-        <v>327</v>
+        <v>393</v>
       </c>
       <c r="E26" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="B27" t="s">
-        <v>325</v>
+        <v>391</v>
       </c>
       <c r="C27" t="s">
-        <v>326</v>
+        <v>392</v>
       </c>
       <c r="D27" t="s">
-        <v>327</v>
+        <v>393</v>
       </c>
       <c r="E27" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>329</v>
+        <v>395</v>
       </c>
       <c r="B28" t="s">
-        <v>330</v>
+        <v>396</v>
       </c>
       <c r="C28" t="s">
         <v>18</v>
       </c>
       <c r="D28" t="s">
-        <v>331</v>
+        <v>397</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>329</v>
+        <v>395</v>
       </c>
       <c r="B29" t="s">
-        <v>330</v>
+        <v>396</v>
       </c>
       <c r="C29" t="s">
         <v>18</v>
       </c>
       <c r="D29" t="s">
-        <v>331</v>
+        <v>397</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>329</v>
+        <v>395</v>
       </c>
       <c r="B30" t="s">
-        <v>330</v>
+        <v>396</v>
       </c>
       <c r="C30" t="s">
         <v>18</v>
       </c>
       <c r="D30" t="s">
-        <v>331</v>
+        <v>397</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>329</v>
+        <v>395</v>
       </c>
       <c r="B32" t="s">
-        <v>330</v>
+        <v>396</v>
       </c>
       <c r="C32" t="s">
         <v>18</v>
       </c>
       <c r="D32" t="s">
-        <v>331</v>
+        <v>397</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>329</v>
+        <v>395</v>
       </c>
       <c r="B33" t="s">
-        <v>330</v>
+        <v>396</v>
       </c>
       <c r="C33" t="s">
         <v>18</v>
       </c>
       <c r="D33" t="s">
-        <v>331</v>
+        <v>397</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>332</v>
+        <v>398</v>
       </c>
       <c r="B34" t="s">
-        <v>333</v>
+        <v>399</v>
       </c>
       <c r="C34" t="s">
-        <v>334</v>
+        <v>400</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>329</v>
+        <v>395</v>
       </c>
       <c r="B35" t="s">
-        <v>330</v>
+        <v>396</v>
       </c>
       <c r="C35" t="s">
         <v>18</v>
       </c>
       <c r="D35" t="s">
-        <v>331</v>
+        <v>397</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>329</v>
+        <v>395</v>
       </c>
       <c r="B36" t="s">
-        <v>330</v>
+        <v>396</v>
       </c>
       <c r="C36" t="s">
         <v>18</v>
       </c>
       <c r="D36" t="s">
-        <v>331</v>
+        <v>397</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -4094,363 +4772,569 @@
         <v>18</v>
       </c>
       <c r="B37" t="s">
-        <v>335</v>
+        <v>401</v>
       </c>
       <c r="C37" t="s">
-        <v>336</v>
+        <v>402</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="B38" t="s">
-        <v>325</v>
+        <v>391</v>
       </c>
       <c r="C38" t="s">
-        <v>326</v>
+        <v>392</v>
       </c>
       <c r="D38" t="s">
-        <v>327</v>
+        <v>393</v>
       </c>
       <c r="E38" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="B40" t="s">
-        <v>325</v>
+        <v>391</v>
       </c>
       <c r="C40" t="s">
-        <v>326</v>
+        <v>392</v>
       </c>
       <c r="D40" t="s">
-        <v>327</v>
+        <v>393</v>
       </c>
       <c r="E40" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="B41" t="s">
-        <v>325</v>
+        <v>391</v>
       </c>
       <c r="C41" t="s">
-        <v>326</v>
+        <v>392</v>
       </c>
       <c r="D41" t="s">
-        <v>327</v>
+        <v>393</v>
       </c>
       <c r="E41" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="B42" t="s">
-        <v>325</v>
+        <v>391</v>
       </c>
       <c r="C42" t="s">
-        <v>326</v>
+        <v>392</v>
       </c>
       <c r="D42" t="s">
-        <v>327</v>
+        <v>393</v>
       </c>
       <c r="E42" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>329</v>
+        <v>395</v>
       </c>
       <c r="B43" t="s">
-        <v>330</v>
+        <v>396</v>
       </c>
       <c r="C43" t="s">
         <v>18</v>
       </c>
       <c r="D43" t="s">
-        <v>331</v>
+        <v>397</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>329</v>
+        <v>395</v>
       </c>
       <c r="B44" t="s">
-        <v>330</v>
+        <v>396</v>
       </c>
       <c r="C44" t="s">
         <v>18</v>
       </c>
       <c r="D44" t="s">
-        <v>331</v>
+        <v>397</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>329</v>
+        <v>395</v>
       </c>
       <c r="B45" t="s">
-        <v>330</v>
+        <v>396</v>
       </c>
       <c r="C45" t="s">
         <v>18</v>
       </c>
       <c r="D45" t="s">
-        <v>331</v>
+        <v>397</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="B46" t="s">
-        <v>325</v>
+        <v>391</v>
       </c>
       <c r="C46" t="s">
-        <v>326</v>
+        <v>392</v>
       </c>
       <c r="D46" t="s">
-        <v>327</v>
+        <v>393</v>
       </c>
       <c r="E46" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="B47" t="s">
-        <v>325</v>
+        <v>391</v>
       </c>
       <c r="C47" t="s">
-        <v>326</v>
+        <v>392</v>
       </c>
       <c r="D47" t="s">
-        <v>327</v>
+        <v>393</v>
       </c>
       <c r="E47" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="B48" t="s">
-        <v>325</v>
+        <v>391</v>
       </c>
       <c r="C48" t="s">
-        <v>326</v>
+        <v>392</v>
       </c>
       <c r="D48" t="s">
-        <v>327</v>
+        <v>393</v>
       </c>
       <c r="E48" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="B49" t="s">
-        <v>325</v>
+        <v>391</v>
       </c>
       <c r="C49" t="s">
-        <v>326</v>
+        <v>392</v>
       </c>
       <c r="D49" t="s">
-        <v>327</v>
+        <v>393</v>
       </c>
       <c r="E49" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>329</v>
+        <v>395</v>
       </c>
       <c r="B50" t="s">
-        <v>330</v>
+        <v>396</v>
       </c>
       <c r="C50" t="s">
         <v>18</v>
       </c>
       <c r="D50" t="s">
-        <v>331</v>
+        <v>397</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="B51" t="s">
-        <v>325</v>
+        <v>391</v>
       </c>
       <c r="C51" t="s">
-        <v>326</v>
+        <v>392</v>
       </c>
       <c r="D51" t="s">
-        <v>327</v>
+        <v>393</v>
       </c>
       <c r="E51" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="B52" t="s">
-        <v>325</v>
+        <v>391</v>
       </c>
       <c r="C52" t="s">
-        <v>326</v>
+        <v>392</v>
       </c>
       <c r="D52" t="s">
-        <v>327</v>
+        <v>393</v>
       </c>
       <c r="E52" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="B53" t="s">
-        <v>325</v>
+        <v>391</v>
       </c>
       <c r="C53" t="s">
-        <v>326</v>
+        <v>392</v>
       </c>
       <c r="D53" t="s">
-        <v>327</v>
+        <v>393</v>
       </c>
       <c r="E53" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="B54" t="s">
-        <v>325</v>
+        <v>391</v>
       </c>
       <c r="C54" t="s">
-        <v>326</v>
+        <v>392</v>
       </c>
       <c r="D54" t="s">
-        <v>327</v>
+        <v>393</v>
       </c>
       <c r="E54" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="B55" t="s">
-        <v>325</v>
+        <v>391</v>
       </c>
       <c r="C55" t="s">
-        <v>326</v>
+        <v>392</v>
       </c>
       <c r="D55" t="s">
-        <v>327</v>
+        <v>393</v>
       </c>
       <c r="E55" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>329</v>
+        <v>395</v>
       </c>
       <c r="B56" t="s">
-        <v>330</v>
+        <v>396</v>
       </c>
       <c r="C56" t="s">
         <v>18</v>
       </c>
       <c r="D56" t="s">
-        <v>331</v>
+        <v>397</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="B57" t="s">
-        <v>325</v>
+        <v>391</v>
       </c>
       <c r="C57" t="s">
-        <v>326</v>
+        <v>392</v>
       </c>
       <c r="D57" t="s">
-        <v>327</v>
+        <v>393</v>
       </c>
       <c r="E57" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>329</v>
+        <v>395</v>
       </c>
       <c r="B59" t="s">
-        <v>330</v>
+        <v>396</v>
       </c>
       <c r="C59" t="s">
         <v>18</v>
       </c>
       <c r="D59" t="s">
-        <v>331</v>
+        <v>397</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>329</v>
+        <v>395</v>
       </c>
       <c r="B60" t="s">
-        <v>330</v>
+        <v>396</v>
       </c>
       <c r="C60" t="s">
         <v>18</v>
       </c>
       <c r="D60" t="s">
-        <v>331</v>
+        <v>397</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="B61" t="s">
-        <v>325</v>
+        <v>391</v>
       </c>
       <c r="C61" t="s">
-        <v>326</v>
+        <v>392</v>
       </c>
       <c r="D61" t="s">
-        <v>327</v>
+        <v>393</v>
       </c>
       <c r="E61" t="s">
-        <v>328</v>
+        <v>394</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>395</v>
+      </c>
+      <c r="B62" t="s">
+        <v>396</v>
+      </c>
+      <c r="C62" t="s">
+        <v>18</v>
+      </c>
+      <c r="D62" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>390</v>
+      </c>
+      <c r="B63" t="s">
+        <v>391</v>
+      </c>
+      <c r="C63" t="s">
+        <v>392</v>
+      </c>
+      <c r="D63" t="s">
+        <v>393</v>
+      </c>
+      <c r="E63" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>390</v>
+      </c>
+      <c r="B64" t="s">
+        <v>391</v>
+      </c>
+      <c r="C64" t="s">
+        <v>392</v>
+      </c>
+      <c r="D64" t="s">
+        <v>393</v>
+      </c>
+      <c r="E64" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>395</v>
+      </c>
+      <c r="B65" t="s">
+        <v>396</v>
+      </c>
+      <c r="C65" t="s">
+        <v>18</v>
+      </c>
+      <c r="D65" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>390</v>
+      </c>
+      <c r="B66" t="s">
+        <v>391</v>
+      </c>
+      <c r="C66" t="s">
+        <v>392</v>
+      </c>
+      <c r="D66" t="s">
+        <v>393</v>
+      </c>
+      <c r="E66" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>390</v>
+      </c>
+      <c r="B67" t="s">
+        <v>391</v>
+      </c>
+      <c r="C67" t="s">
+        <v>392</v>
+      </c>
+      <c r="D67" t="s">
+        <v>393</v>
+      </c>
+      <c r="E67" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>390</v>
+      </c>
+      <c r="B68" t="s">
+        <v>391</v>
+      </c>
+      <c r="C68" t="s">
+        <v>392</v>
+      </c>
+      <c r="D68" t="s">
+        <v>393</v>
+      </c>
+      <c r="E68" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>395</v>
+      </c>
+      <c r="B69" t="s">
+        <v>396</v>
+      </c>
+      <c r="C69" t="s">
+        <v>18</v>
+      </c>
+      <c r="D69" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>395</v>
+      </c>
+      <c r="B70" t="s">
+        <v>396</v>
+      </c>
+      <c r="C70" t="s">
+        <v>18</v>
+      </c>
+      <c r="D70" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>390</v>
+      </c>
+      <c r="B71" t="s">
+        <v>391</v>
+      </c>
+      <c r="C71" t="s">
+        <v>392</v>
+      </c>
+      <c r="D71" t="s">
+        <v>393</v>
+      </c>
+      <c r="E71" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>390</v>
+      </c>
+      <c r="B72" t="s">
+        <v>391</v>
+      </c>
+      <c r="C72" t="s">
+        <v>392</v>
+      </c>
+      <c r="D72" t="s">
+        <v>393</v>
+      </c>
+      <c r="E72" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>390</v>
+      </c>
+      <c r="B73" t="s">
+        <v>391</v>
+      </c>
+      <c r="C73" t="s">
+        <v>392</v>
+      </c>
+      <c r="D73" t="s">
+        <v>393</v>
+      </c>
+      <c r="E73" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>395</v>
+      </c>
+      <c r="B74" t="s">
+        <v>396</v>
+      </c>
+      <c r="C74" t="s">
+        <v>18</v>
+      </c>
+      <c r="D74" t="s">
+        <v>397</v>
       </c>
     </row>
   </sheetData>

--- a/seed/question-bank/source/TPL-002_Internal_Data_Handlers.xlsx
+++ b/seed/question-bank/source/TPL-002_Internal_Data_Handlers.xlsx
@@ -1031,13 +1031,13 @@
     <t>c0000001-bc00-0000-0000-000000000001</t>
   </si>
   <si>
-    <t>School Operations</t>
+    <t>Education Operations</t>
   </si>
   <si>
     <t>B12.1</t>
   </si>
   <si>
-    <t>Is a parent's or lawful guardian's verifiable consent obtained before a student's personal data is processed on the basis of consent?</t>
+    <t>For students under 18, is a parent's or lawful guardian's verifiable consent obtained before their personal data is processed on the basis of consent?</t>
   </si>
   <si>
     <t>HIGH</t>
@@ -1047,8 +1047,8 @@
   </si>
   <si>
     <t xml:space="preserve">Admission form with the parental consent section
-Consent records for each student
-How the school checks that the person consenting is the parent or guardian and an adult</t>
+Consent records for students under 18
+How the institution checks that the person consenting is the parent or guardian and an adult</t>
   </si>
   <si>
     <t>c0000002-bc00-0000-0000-000000000001</t>
@@ -1057,7 +1057,7 @@
     <t>B12.2</t>
   </si>
   <si>
-    <t>Does the admission process collect only the student and parent data the school needs, with a notice that lists that data and its purposes?</t>
+    <t>Does the admission process collect only the student and parent data the institution needs, with a notice that lists that data and its purposes?</t>
   </si>
   <si>
     <t>MEDIUM</t>
@@ -1074,7 +1074,7 @@
     <t>B12.3</t>
   </si>
   <si>
-    <t>Is tracking or behavioural monitoring of students (classroom CCTV, bus GPS, attendance or learning apps) limited to educational activities and student safety?</t>
+    <t>Is tracking or behavioural monitoring of students under 18 (classroom CCTV, bus GPS, attendance or learning apps) limited to educational activities and their safety?</t>
   </si>
   <si>
     <t>S.9(3), S.9(4), Rule 12, Fourth Schedule</t>
@@ -1091,7 +1091,7 @@
     <t>B12.4</t>
   </si>
   <si>
-    <t>Are students' data kept from advertising, marketing and any use detrimental to their well-being, including promotions by ed-tech, uniform or book vendors?</t>
+    <t>Are students' data kept from advertising, marketing and any use detrimental to their well-being, including promotions by ed-tech, coaching, uniform or book vendors?</t>
   </si>
   <si>
     <t>S.9(2), S.9(3)</t>
@@ -1108,7 +1108,7 @@
     <t>B12.5</t>
   </si>
   <si>
-    <t>Is school transport data (routes, stops, pick-up times, GPS tracking, driver and attendant details) access-controlled and shared only with parents and authorised staff?</t>
+    <t>Is student transport data (routes, stops, pick-up times, GPS tracking, driver and attendant details) access-controlled and shared only with parents, students and authorised staff?</t>
   </si>
   <si>
     <t>S.8(5), Rule 6, Fourth Schedule</t>
@@ -1125,7 +1125,7 @@
     <t>B12.6</t>
   </si>
   <si>
-    <t>Are students' health records (medical room visits, allergies, vaccinations, special needs) kept confidential and open only to the staff who need them?</t>
+    <t>Are students' health records (medical room or health centre visits, allergies, vaccinations, special needs) kept confidential and open only to the staff who need them?</t>
   </si>
   <si>
     <t>S.8(5), Rule 6</t>
@@ -1142,7 +1142,7 @@
     <t>B12.7</t>
   </si>
   <si>
-    <t>Are counselling, disciplinary and child-protection (POCSO) records kept separately, with access restricted to the designated staff?</t>
+    <t>Are counselling, disciplinary, anti-ragging, internal complaints and child-protection (POCSO) records kept separately, with access restricted to the designated staff?</t>
   </si>
   <si>
     <t>S.8(5), S.9(2), Rule 6</t>
@@ -1159,7 +1159,7 @@
     <t>B12.8</t>
   </si>
   <si>
-    <t>Are photos and videos of students published (website, social media, newsletters) only with parental consent, and taken down when consent is withdrawn?</t>
+    <t>Are photos and videos of students published (website, social media, newsletters, brochures) only with consent (a parent or guardian for students under 18), and taken down when it is withdrawn?</t>
   </si>
   <si>
     <t>S.6(4), S.9(1)</t>
@@ -1176,7 +1176,7 @@
     <t>B12.9</t>
   </si>
   <si>
-    <t>Are student and parent records shared with boards, government portals and ed-tech or transport vendors only where a law requires it or under a contract?</t>
+    <t>Are student and parent records shared with boards, universities, regulators, government portals and ed-tech, placement or transport vendors only where a law requires it or under a contract?</t>
   </si>
   <si>
     <t>S.7, S.8(2)</t>
@@ -1192,7 +1192,7 @@
     <t>B12.10</t>
   </si>
   <si>
-    <t>Is there a retention schedule for admission, academic, fee and transfer records, including applicants not admitted and students who have left?</t>
+    <t>Is there a retention schedule for admission, academic, examination, fee and transfer records, including applicants not admitted and students who have left?</t>
   </si>
   <si>
     <t xml:space="preserve">Retention schedule for student records
@@ -1206,13 +1206,13 @@
     <t>B12.11</t>
   </si>
   <si>
-    <t>Can parents ask to see, correct or erase their child's data and raise grievances, and does the school verify that the request comes from the parent or guardian?</t>
+    <t>Can students, or the parents of students under 18, ask to see, correct or erase the data and raise grievances, and does the institution verify who is asking?</t>
   </si>
   <si>
     <t>S.11-S.13, Rule 14</t>
   </si>
   <si>
-    <t xml:space="preserve">Rights request form or channel for parents
+    <t xml:space="preserve">Rights request form or channel for students and parents
 Requester verification procedure
 Rights and grievance request log</t>
   </si>
@@ -1240,7 +1240,7 @@
     <t>B12.13</t>
   </si>
   <si>
-    <t>Are student accounts on learning platforms and school apps set up without behavioural profiling or targeted advertising, and are the vendor terms checked for this?</t>
+    <t>Are student accounts on learning platforms and institution apps set up without behavioural profiling or targeted advertising of students under 18, and are the vendor terms checked for this?</t>
   </si>
   <si>
     <t>S.9(3), S.8(2)</t>
